--- a/task149/golden/ergonomics_forecast_fy2027.xlsx
+++ b/task149/golden/ergonomics_forecast_fy2027.xlsx
@@ -471,7 +471,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Expected cases with a date of injury in fiscal 2027 on the FY2027 operating plan v3 volumes and labor hours, rounded to the nearest hundred (agreement Schedule B 2.1 to 2.3)</t>
+          <t>Expected cases with a date of injury in fiscal 2027 under the FY2027 operating plan v3 (approved 10/23/2026), rounded to the nearest hundred (agreement Schedule B 2.1 to 2.3)</t>
         </is>
       </c>
     </row>
